--- a/Result/profitability/1457.xlsx
+++ b/Result/profitability/1457.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2812500000000001</v>
+        <v>0.2437500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.81</v>
+        <v>8.883750000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2000000000000001</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>7.86</v>
+        <v>8.046250000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2112500000000001</v>
+        <v>0.1987500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>6.928750000000001</v>
+        <v>7.108750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.95</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0337500000000001</v>
+        <v>0.09000000000000011</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84125</v>
+        <v>2.91</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05125000000000011</v>
+        <v>0.09250000000000011</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9675</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04875000000000011</v>
+        <v>0.002500000000000118</v>
       </c>
       <c r="N7" t="n">
-        <v>1.38375</v>
+        <v>2.0075</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03374999999999989</v>
+        <v>-0.01249999999999988</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9624999999999999</v>
+        <v>1.71375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.01</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05749999999999989</v>
+        <v>-0.05749999999999988</v>
       </c>
       <c r="N9" t="n">
         <v>1.0675</v>
@@ -1645,7 +1645,7 @@
         <v>0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.05874999999999988</v>
+        <v>-0.05874999999999989</v>
       </c>
       <c r="N10" t="n">
         <v>1.235</v>
@@ -2029,7 +2029,7 @@
         <v>0.1987500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7825</v>
+        <v>5.782500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>781</v>
+      </c>
+      <c r="D75" t="n">
+        <v>688</v>
+      </c>
+      <c r="E75" t="n">
+        <v>93</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="G75" t="n">
+        <v>54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>109</v>
+      </c>
+      <c r="J75" t="n">
+        <v>162</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2975000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.693750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8499999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.015202702702703</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5499999999999989</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.048330404217926</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
